--- a/seminar_02/problem_2.9_solution.xlsx
+++ b/seminar_02/problem_2.9_solution.xlsx
@@ -631,9 +631,10 @@
         <f>COUNT(B5:B14)</f>
         <v/>
       </c>
-      <c r="I5" s="7">
-        <f>СЧЁТ(B5:B14)</f>
-        <v/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>=СЧЁТ(B5:B14)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -663,9 +664,10 @@
         <f>SUM(C5:C14)</f>
         <v/>
       </c>
-      <c r="I6" s="7">
-        <f>СУММ(C5:C14)</f>
-        <v/>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>=СУММ(C5:C14)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -695,9 +697,10 @@
         <f>SUM(B5:B14)</f>
         <v/>
       </c>
-      <c r="I7" s="7">
-        <f>СУММ(B5:B14)</f>
-        <v/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>=СУММ(B5:B14)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -727,9 +730,10 @@
         <f>SUMSQ(C5:C14)</f>
         <v/>
       </c>
-      <c r="I8" s="7">
-        <f>СУММКВ(C5:C14)</f>
-        <v/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>=СУММКВ(C5:C14)</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -759,9 +763,10 @@
         <f>SUMSQ(B5:B14)</f>
         <v/>
       </c>
-      <c r="I9" s="7">
-        <f>СУММКВ(B5:B14)</f>
-        <v/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>=СУММКВ(B5:B14)</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -791,9 +796,10 @@
         <f>SUMPRODUCT(B5:B14,C5:C14)</f>
         <v/>
       </c>
-      <c r="I10" s="7">
-        <f>СУММПРОИЗВ(B5:B14;C5:C14)</f>
-        <v/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>=СУММПРОИЗВ(B5:B14;C5:C14)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -823,9 +829,10 @@
         <f>AVERAGE(C5:C14)</f>
         <v/>
       </c>
-      <c r="I11" s="7">
-        <f>СРЗНАЧ(C5:C14)</f>
-        <v/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>=СРЗНАЧ(C5:C14)</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -855,9 +862,10 @@
         <f>AVERAGE(B5:B14)</f>
         <v/>
       </c>
-      <c r="I12" s="7">
-        <f>СРЗНАЧ(B5:B14)</f>
-        <v/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>=СРЗНАЧ(B5:B14)</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -887,9 +895,10 @@
         <f>SUMSQ(D5:D14)</f>
         <v/>
       </c>
-      <c r="I13" s="7">
-        <f>СУММКВ(D5:D14)</f>
-        <v/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>=СУММКВ(D5:D14)</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -919,9 +928,10 @@
         <f>SUMPRODUCT(D5:D14,E5:E14)</f>
         <v/>
       </c>
-      <c r="I14" s="7">
-        <f>СУММПРОИЗВ(D5:D14;E5:E14)</f>
-        <v/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>=СУММПРОИЗВ(D5:D14;E5:E14)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -955,9 +965,10 @@
         <f>SUMSQ(E5:E14)</f>
         <v/>
       </c>
-      <c r="I15" s="7">
-        <f>СУММКВ(E5:E14)</f>
-        <v/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>=СУММКВ(E5:E14)</t>
+        </is>
       </c>
     </row>
     <row r="16">
